--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.94567558160635</v>
+        <v>5.516172282011032</v>
       </c>
       <c r="D2" t="n">
-        <v>20.08024090920363</v>
+        <v>3.26303914774559</v>
       </c>
       <c r="E2" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F2" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.24063004653979</v>
+        <v>6.214102382562716</v>
       </c>
       <c r="D3" t="n">
-        <v>25.68529703839566</v>
+        <v>4.173860768739295</v>
       </c>
       <c r="E3" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F3" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.01274378823791</v>
+        <v>6.01457086558866</v>
       </c>
       <c r="D4" t="n">
-        <v>25.43328618236896</v>
+        <v>4.132909004634955</v>
       </c>
       <c r="E4" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F4" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.42365979492737</v>
+        <v>3.643844716675697</v>
       </c>
       <c r="D5" t="n">
-        <v>14.80715331376593</v>
+        <v>2.406162413486964</v>
       </c>
       <c r="E5" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F5" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.28785651194103</v>
+        <v>2.321776683190417</v>
       </c>
       <c r="D6" t="n">
-        <v>14.17475490282204</v>
+        <v>2.303397671708582</v>
       </c>
       <c r="E6" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F6" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>56.11748202260316</v>
+        <v>9.119090828673013</v>
       </c>
       <c r="D7" t="n">
-        <v>15.65246958392557</v>
+        <v>2.543526307387905</v>
       </c>
       <c r="E7" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F7" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>45.06303384684713</v>
+        <v>7.322743000112659</v>
       </c>
       <c r="D8" t="n">
-        <v>44.95135936457125</v>
+        <v>7.304595896742827</v>
       </c>
       <c r="E8" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F8" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>61.45242373691832</v>
+        <v>9.986018857249228</v>
       </c>
       <c r="D9" t="n">
-        <v>67.94251664474025</v>
+        <v>11.04065895477029</v>
       </c>
       <c r="E9" t="n">
-        <v>14.78142245409332</v>
+        <v>2.401981148790164</v>
       </c>
       <c r="F9" t="n">
-        <v>17.57938646799431</v>
+        <v>2.856650301049076</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
